--- a/tables/GAM_subregions_20260516_ed.xlsx
+++ b/tables/GAM_subregions_20260516_ed.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulavaldti-my.sharepoint.com/personal/papat21_ulaval_ca/Documents/Laval_Postdoc/R_Worskapce/Laval_Arctic_Traits/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{7E55ABCB-E985-45C7-8188-45031F5CE9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{829A164B-A98D-4926-A014-76DA4191FA48}"/>
+  <xr:revisionPtr revIDLastSave="552" documentId="8_{7E55ABCB-E985-45C7-8188-45031F5CE9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C05072E-F22F-461A-8FA6-89390ABC2871}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{B1F5A884-24C5-4ABA-A891-336B70B7A1CB}"/>
   </bookViews>
   <sheets>
-    <sheet name="GAM_subregions_20260516" sheetId="1" r:id="rId1"/>
+    <sheet name="Complete GAM results" sheetId="2" r:id="rId1"/>
+    <sheet name="GAM_subregions_20260516" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="71">
   <si>
     <t>n</t>
   </si>
@@ -143,13 +144,151 @@
   </si>
   <si>
     <t>beta estimate</t>
+  </si>
+  <si>
+    <t>Parametric terms</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>(Intercept)</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Ref.df</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>***</t>
+  </si>
+  <si>
+    <t>Smooth terms</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>Std. Error</t>
+  </si>
+  <si>
+    <t>Parametric term</t>
+  </si>
+  <si>
+    <t>Smooth term</t>
+  </si>
+  <si>
+    <t>Deviance explained</t>
+  </si>
+  <si>
+    <t>GAM terms and fits</t>
+  </si>
+  <si>
+    <t>day of year</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>s(bottom depth)</t>
+  </si>
+  <si>
+    <t>s(latitude, k = 5)</t>
+  </si>
+  <si>
+    <t>1.) LPC flux of all profiles (n = 208)</t>
+  </si>
+  <si>
+    <t>2.) Daily POC flux of all valid profiles deeper than 200 m (n = 148)</t>
+  </si>
+  <si>
+    <t>3.) LPC flux of Nares Strait profiles (n = 23)</t>
+  </si>
+  <si>
+    <t>4.) LPC flux of Pikialasorsuaq profiles (n = 63)</t>
+  </si>
+  <si>
+    <t>5.) LPC flux of Tallurutiup Imanga profiles (n = 33)</t>
+  </si>
+  <si>
+    <t>6.) LPC flux of Sannirutiup Imavik profiles (n = 21)</t>
+  </si>
+  <si>
+    <t>7.) LPC flux of Qikiqtaaluup Ikinga profiles (n = 33)</t>
+  </si>
+  <si>
+    <t>8.) LPC flux of Qikiqtaaluuk Shelf profiles (n = 24)</t>
+  </si>
+  <si>
+    <t>9.) LPC flux of Nunatsavut Shelf profiles (n = 11)</t>
+  </si>
+  <si>
+    <r>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>adj</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>p-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>value</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="179" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,8 +423,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="superscript"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -465,8 +641,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -581,6 +763,149 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -626,11 +951,122 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="179" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="21" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="21" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1005,6 +1441,1050 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{663CDCC5-2F97-4BA5-9BC8-C5C682BC4FCA}">
+  <dimension ref="C1:K43"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.19921875" customWidth="1"/>
+    <col min="3" max="3" width="14.1328125" customWidth="1"/>
+    <col min="4" max="4" width="7.53125" customWidth="1"/>
+    <col min="5" max="5" width="8.86328125" customWidth="1"/>
+    <col min="6" max="6" width="16.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="9.06640625" style="3"/>
+    <col min="11" max="11" width="4.53125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:11" ht="26.65" x14ac:dyDescent="0.5">
+      <c r="C1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+    </row>
+    <row r="2" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C2" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0.43</v>
+      </c>
+      <c r="E2" s="7">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" s="23"/>
+    </row>
+    <row r="3" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C3" s="33"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="10">
+        <v>325.71751999999998</v>
+      </c>
+      <c r="H3" s="10">
+        <v>276.41244</v>
+      </c>
+      <c r="I3" s="17">
+        <v>1.1779999999999999</v>
+      </c>
+      <c r="J3" s="24">
+        <v>0.24010000000000001</v>
+      </c>
+      <c r="K3" s="25"/>
+    </row>
+    <row r="4" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C4" s="33"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="10">
+        <v>-1.09E-2</v>
+      </c>
+      <c r="H4" s="10">
+        <v>5.28E-3</v>
+      </c>
+      <c r="I4" s="17">
+        <v>-2.0640000000000001</v>
+      </c>
+      <c r="J4" s="24">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C5" s="33"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="10">
+        <v>-0.15833</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0.13653000000000001</v>
+      </c>
+      <c r="I5" s="17">
+        <v>-1.1599999999999999</v>
+      </c>
+      <c r="J5" s="24">
+        <v>0.24759999999999999</v>
+      </c>
+      <c r="K5" s="25"/>
+    </row>
+    <row r="6" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C6" s="33"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" s="27"/>
+    </row>
+    <row r="7" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C7" s="33"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="10">
+        <v>4.0309999999999997</v>
+      </c>
+      <c r="H7" s="10">
+        <v>4.9480000000000004</v>
+      </c>
+      <c r="I7" s="17">
+        <v>19.140999999999998</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C8" s="33"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="10">
+        <v>3.7370000000000001</v>
+      </c>
+      <c r="H8" s="10">
+        <v>4.5359999999999996</v>
+      </c>
+      <c r="I8" s="17">
+        <v>6.7720000000000002</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C9" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="34">
+        <v>0.24</v>
+      </c>
+      <c r="E9" s="37">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="25"/>
+    </row>
+    <row r="10" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="11">
+        <v>-9303</v>
+      </c>
+      <c r="H10" s="11">
+        <v>3275</v>
+      </c>
+      <c r="I10" s="18">
+        <v>-2.84</v>
+      </c>
+      <c r="J10" s="29">
+        <v>5.1700000000000001E-3</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="10">
+        <v>6.4549999999999996E-2</v>
+      </c>
+      <c r="H11" s="10">
+        <v>6.207E-2</v>
+      </c>
+      <c r="I11" s="18">
+        <v>1.04</v>
+      </c>
+      <c r="J11" s="24">
+        <v>0.30010999999999999</v>
+      </c>
+      <c r="K11" s="25"/>
+    </row>
+    <row r="12" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="10">
+        <v>4.5979999999999999</v>
+      </c>
+      <c r="H12" s="10">
+        <v>1.6180000000000001</v>
+      </c>
+      <c r="I12" s="17">
+        <v>2.8420000000000001</v>
+      </c>
+      <c r="J12" s="29">
+        <v>5.1500000000000001E-3</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13" s="25"/>
+    </row>
+    <row r="14" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="10">
+        <v>1.502</v>
+      </c>
+      <c r="H14" s="10">
+        <v>1.853</v>
+      </c>
+      <c r="I14" s="17">
+        <v>3.246</v>
+      </c>
+      <c r="J14" s="24">
+        <v>3.2329999999999998E-2</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="10">
+        <v>2.698</v>
+      </c>
+      <c r="H15" s="10">
+        <v>3.157</v>
+      </c>
+      <c r="I15" s="17">
+        <v>4.3140000000000001</v>
+      </c>
+      <c r="J15" s="29">
+        <v>6.3400000000000001E-3</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C16" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="40">
+        <v>-3.10657729420982E-2</v>
+      </c>
+      <c r="E16" s="37">
+        <v>1.5105800000000001E-2</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="J16" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K16" s="25"/>
+    </row>
+    <row r="17" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C17" s="35"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0.77046950043032802</v>
+      </c>
+      <c r="H17" s="10">
+        <v>8.2065041779643202E-2</v>
+      </c>
+      <c r="I17" s="17">
+        <v>9.3885226123341692</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C18" s="35"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="K18" s="25"/>
+    </row>
+    <row r="19" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C19" s="36"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" s="10">
+        <v>1</v>
+      </c>
+      <c r="H19" s="10">
+        <v>1</v>
+      </c>
+      <c r="I19" s="17">
+        <v>0.32</v>
+      </c>
+      <c r="J19" s="24">
+        <v>0.57657000000000003</v>
+      </c>
+      <c r="K19" s="25"/>
+    </row>
+    <row r="20" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C20" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="40">
+        <v>0.34908467499460399</v>
+      </c>
+      <c r="E20" s="37">
+        <v>0.35958457393495402</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J20" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20" s="25"/>
+    </row>
+    <row r="21" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C21" s="35"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="10">
+        <v>2.6646426877893901</v>
+      </c>
+      <c r="H21" s="10">
+        <v>0.15285432121909101</v>
+      </c>
+      <c r="I21" s="17">
+        <v>17.4325636759073</v>
+      </c>
+      <c r="J21" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C22" s="35"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="K22" s="25"/>
+    </row>
+    <row r="23" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C23" s="36"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="10">
+        <v>1.0001204600556299</v>
+      </c>
+      <c r="H23" s="10">
+        <v>1.0002409056006401</v>
+      </c>
+      <c r="I23" s="17">
+        <v>34.243011768125101</v>
+      </c>
+      <c r="J23" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C24" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="40">
+        <v>0.69756399999999996</v>
+      </c>
+      <c r="E24" s="37">
+        <v>0.73034969999999999</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J24" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K24" s="25"/>
+    </row>
+    <row r="25" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C25" s="35"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="10">
+        <v>1.8652074748220999</v>
+      </c>
+      <c r="H25" s="10">
+        <v>0.12933466794806101</v>
+      </c>
+      <c r="I25" s="17">
+        <v>14.421558460807599</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C26" s="35"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K26" s="25"/>
+    </row>
+    <row r="27" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C27" s="36"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27" s="10">
+        <v>3.47</v>
+      </c>
+      <c r="H27" s="10">
+        <v>4.16</v>
+      </c>
+      <c r="I27" s="17">
+        <v>17.86</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C28" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="40">
+        <v>9.6360000000000001E-2</v>
+      </c>
+      <c r="E28" s="37">
+        <v>0.1850368</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I28" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K28" s="25"/>
+    </row>
+    <row r="29" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C29" s="35"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G29" s="10">
+        <v>3.1865334755666899</v>
+      </c>
+      <c r="H29" s="10">
+        <v>0.26507461484621297</v>
+      </c>
+      <c r="I29" s="17">
+        <v>12.0212698504359</v>
+      </c>
+      <c r="J29" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K29" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C30" s="35"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I30" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K30" s="25"/>
+    </row>
+    <row r="31" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C31" s="36"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31" s="10">
+        <v>1.9625999999999999</v>
+      </c>
+      <c r="H31" s="10">
+        <v>2.4060000000000001</v>
+      </c>
+      <c r="I31" s="17">
+        <v>1.4217</v>
+      </c>
+      <c r="J31" s="24">
+        <v>0.31186999999999998</v>
+      </c>
+      <c r="K31" s="25"/>
+    </row>
+    <row r="32" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C32" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="40">
+        <v>0.27359899999999998</v>
+      </c>
+      <c r="E32" s="37">
+        <v>0.31843450000000001</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J32" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K32" s="25"/>
+    </row>
+    <row r="33" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C33" s="35"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="10">
+        <v>3.3811392322145699</v>
+      </c>
+      <c r="H33" s="10">
+        <v>0.21400453552704901</v>
+      </c>
+      <c r="I33" s="17">
+        <v>15.7993811854853</v>
+      </c>
+      <c r="J33" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K33" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C34" s="35"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J34" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K34" s="25"/>
+    </row>
+    <row r="35" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C35" s="36"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" s="10">
+        <v>1.9751000000000001</v>
+      </c>
+      <c r="H35" s="10">
+        <v>2.4976150000000001</v>
+      </c>
+      <c r="I35" s="17">
+        <v>4.49648</v>
+      </c>
+      <c r="J35" s="29">
+        <v>8.4936999999999999E-3</v>
+      </c>
+      <c r="K35" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C36" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="40">
+        <v>0.41258589000000001</v>
+      </c>
+      <c r="E36" s="37">
+        <v>0.4577464</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J36" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K36" s="25"/>
+    </row>
+    <row r="37" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C37" s="35"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G37" s="10">
+        <v>3.1790185838822702</v>
+      </c>
+      <c r="H37" s="10">
+        <v>0.472569149601205</v>
+      </c>
+      <c r="I37" s="17">
+        <v>6.7270971593575197</v>
+      </c>
+      <c r="J37" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K37" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C38" s="35"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I38" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="J38" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="K38" s="25"/>
+    </row>
+    <row r="39" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C39" s="36"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39" s="10">
+        <v>1.768246</v>
+      </c>
+      <c r="H39" s="10">
+        <v>2.1957019999999998</v>
+      </c>
+      <c r="I39" s="17">
+        <v>7.7756216</v>
+      </c>
+      <c r="J39" s="29">
+        <v>2.5070359999999998E-3</v>
+      </c>
+      <c r="K39" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C40" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="40">
+        <v>0.34513108999999997</v>
+      </c>
+      <c r="E40" s="37">
+        <v>0.41061969999999998</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J40" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K40" s="25"/>
+    </row>
+    <row r="41" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C41" s="35"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G41" s="10">
+        <v>4.1502855633142701</v>
+      </c>
+      <c r="H41" s="10">
+        <v>0.59168264442742802</v>
+      </c>
+      <c r="I41" s="17">
+        <v>7.01437772833527</v>
+      </c>
+      <c r="J41" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K41" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="3:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C42" s="35"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I42" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J42" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K42" s="25"/>
+    </row>
+    <row r="43" spans="3:11" x14ac:dyDescent="0.45">
+      <c r="C43" s="36"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43" s="10">
+        <v>1.00001273740588</v>
+      </c>
+      <c r="H43" s="10">
+        <v>1.0000254746495101</v>
+      </c>
+      <c r="I43" s="17">
+        <v>6.2699547999999998</v>
+      </c>
+      <c r="J43" s="31">
+        <v>3.3636319999999997E-2</v>
+      </c>
+      <c r="K43" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="C36:C39"/>
+    <mergeCell ref="D36:D39"/>
+    <mergeCell ref="E36:E39"/>
+    <mergeCell ref="E40:E43"/>
+    <mergeCell ref="D40:D43"/>
+    <mergeCell ref="C40:C43"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="E28:E31"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="D32:D35"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="E20:E23"/>
+    <mergeCell ref="E24:E27"/>
+    <mergeCell ref="D24:D27"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="C9:C15"/>
+    <mergeCell ref="D9:D15"/>
+    <mergeCell ref="E9:E15"/>
+    <mergeCell ref="E16:E19"/>
+    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="E2:E8"/>
+    <mergeCell ref="D2:D8"/>
+    <mergeCell ref="C2:C8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AAA65BA-3305-49EE-A903-63E5AAC464B3}">
   <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1659,7 +3139,7 @@
       <c r="J22">
         <v>2.8450000000000002</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22">
         <v>4.63</v>
       </c>
       <c r="L22">
